--- a/scripts/example_input/voorbeeld_dierlijke_graverij.xlsx
+++ b/scripts/example_input/voorbeeld_dierlijke_graverij.xlsx
@@ -1,8 +1,8 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SAKA\sources\github\faalkansbeheer\scripts\example_input\"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -476,13 +476,13 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="11" xfId="2" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="11" fontId="2" fillId="2" borderId="9" xfId="2" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="11" fontId="2" fillId="2" borderId="11" xfId="2" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="11" fontId="2" fillId="2" borderId="11" xfId="2" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Invoer" xfId="2" builtinId="20"/>
@@ -918,10 +918,10 @@
     </row>
     <row r="2" spans="1:13" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A4" s="19" t="s">
+      <c r="A4" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="B4" s="19"/>
+      <c r="B4" s="20"/>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
@@ -996,10 +996,10 @@
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A11" s="20" t="s">
+      <c r="A11" s="21" t="s">
         <v>43</v>
       </c>
-      <c r="B11" s="20"/>
+      <c r="B11" s="21"/>
       <c r="C11" t="s">
         <v>15</v>
       </c>
@@ -1200,10 +1200,10 @@
       <c r="K20" s="10"/>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A24" s="20" t="s">
+      <c r="A24" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="B24" s="20"/>
+      <c r="B24" s="21"/>
       <c r="E24" t="s">
         <v>20</v>
       </c>
@@ -2053,7 +2053,7 @@
       <c r="A7" s="15">
         <v>5</v>
       </c>
-      <c r="B7" s="21">
+      <c r="B7" s="19">
         <v>1E-3</v>
       </c>
     </row>
@@ -2063,41 +2063,65 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="edfbc03d-db26-4301-8719-99148ee26221">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <n3c4235fe90e4626a88beeb52e343114 xmlns="338e11dd-9b15-475b-8471-fcb79439c886">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-        <TermInfo xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-          <TermName xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">Concept</TermName>
-          <TermId xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">c1e89abd-99d3-43d9-9ea5-d87afe83fe15</TermId>
-        </TermInfo>
-      </Terms>
-    </n3c4235fe90e4626a88beeb52e343114>
-    <e39ed97c196f40ca8994d73dd80b64d0 xmlns="338e11dd-9b15-475b-8471-fcb79439c886">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-        <TermInfo xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-          <TermName xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">Waterschap Rivierenland</TermName>
-          <TermId xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">d1732778-9e42-4ec7-9c76-7a14861f4695</TermId>
-        </TermInfo>
-      </Terms>
-    </e39ed97c196f40ca8994d73dd80b64d0>
-    <TaxCatchAll xmlns="338e11dd-9b15-475b-8471-fcb79439c886">
-      <Value>2</Value>
-      <Value>1</Value>
-    </TaxCatchAll>
-    <_dlc_DocId xmlns="338e11dd-9b15-475b-8471-fcb79439c886">CBPJ-627581585-33370</_dlc_DocId>
-    <_dlc_DocIdUrl xmlns="338e11dd-9b15-475b-8471-fcb79439c886">
-      <Url>https://wsrlnl.sharepoint.com/sites/CBPR-ydjk6ItuUw/_layouts/15/DocIdRedir.aspx?ID=CBPJ-627581585-33370</Url>
-      <Description>CBPJ-627581585-33370</Description>
-    </_dlc_DocIdUrl>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<spe:Receivers xmlns:spe="http://schemas.microsoft.com/sharepoint/events">
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10001</Type>
+    <SequenceNumber>1000</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10002</Type>
+    <SequenceNumber>1001</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10004</Type>
+    <SequenceNumber>1002</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10006</Type>
+    <SequenceNumber>1003</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+</spe:Receivers>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document CB" ma:contentTypeID="0x010100A075C07AB76F2344B407AD577D6B92360100C7929242D85FED4E837C6D4097594A04" ma:contentTypeVersion="16" ma:contentTypeDescription="WSRL Document CB" ma:contentTypeScope="" ma:versionID="88fe53b6e98c5417adee0db248f913ae">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="338e11dd-9b15-475b-8471-fcb79439c886" xmlns:ns3="edfbc03d-db26-4301-8719-99148ee26221" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="d69b3a9fc9dd1d280a5efa296263df02" ns2:_="" ns3:_="">
     <xsd:import namespace="338e11dd-9b15-475b-8471-fcb79439c886"/>
@@ -2373,83 +2397,58 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<spe:Receivers xmlns:spe="http://schemas.microsoft.com/sharepoint/events">
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10001</Type>
-    <SequenceNumber>1000</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10002</Type>
-    <SequenceNumber>1001</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10004</Type>
-    <SequenceNumber>1002</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10006</Type>
-    <SequenceNumber>1003</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-</spe:Receivers>
-</file>
-
 <file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="edfbc03d-db26-4301-8719-99148ee26221">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <n3c4235fe90e4626a88beeb52e343114 xmlns="338e11dd-9b15-475b-8471-fcb79439c886">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+        <TermInfo xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+          <TermName xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">Concept</TermName>
+          <TermId xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">c1e89abd-99d3-43d9-9ea5-d87afe83fe15</TermId>
+        </TermInfo>
+      </Terms>
+    </n3c4235fe90e4626a88beeb52e343114>
+    <e39ed97c196f40ca8994d73dd80b64d0 xmlns="338e11dd-9b15-475b-8471-fcb79439c886">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+        <TermInfo xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+          <TermName xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">Waterschap Rivierenland</TermName>
+          <TermId xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">d1732778-9e42-4ec7-9c76-7a14861f4695</TermId>
+        </TermInfo>
+      </Terms>
+    </e39ed97c196f40ca8994d73dd80b64d0>
+    <TaxCatchAll xmlns="338e11dd-9b15-475b-8471-fcb79439c886">
+      <Value>2</Value>
+      <Value>1</Value>
+    </TaxCatchAll>
+    <_dlc_DocId xmlns="338e11dd-9b15-475b-8471-fcb79439c886">CBPJ-627581585-33370</_dlc_DocId>
+    <_dlc_DocIdUrl xmlns="338e11dd-9b15-475b-8471-fcb79439c886">
+      <Url>https://wsrlnl.sharepoint.com/sites/CBPR-ydjk6ItuUw/_layouts/15/DocIdRedir.aspx?ID=CBPJ-627581585-33370</Url>
+      <Description>CBPJ-627581585-33370</Description>
+    </_dlc_DocIdUrl>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8FA96AA6-3687-4803-9D38-8F86AB3B850C}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{78F48322-4FD1-4D94-BEE5-6BE781D24505}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="338e11dd-9b15-475b-8471-fcb79439c886"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="edfbc03d-db26-4301-8719-99148ee26221"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A138CF7A-8662-4303-935C-7BE86E2888FE}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/events"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3691F1F7-72B1-41D9-8657-9C07AFE6AA73}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2468,18 +2467,19 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A138CF7A-8662-4303-935C-7BE86E2888FE}">
+<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8FA96AA6-3687-4803-9D38-8F86AB3B850C}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/events"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{78F48322-4FD1-4D94-BEE5-6BE781D24505}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="338e11dd-9b15-475b-8471-fcb79439c886"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="edfbc03d-db26-4301-8719-99148ee26221"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>